--- a/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
+++ b/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CBAFEE-4EC2-42CC-B05A-BA5D75183754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA967D3-44E9-4772-9720-7DDE2B17EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,23 +98,23 @@
     <t>The five single FK values and all array FK values reference rows from the previously generated TestTable data.</t>
   </si>
   <si>
-    <t>Ref01</t>
+    <t>Ref_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ref02</t>
+    <t>Ref_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ref03</t>
+    <t>Ref_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ref04</t>
+    <t>Ref_04</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ref05</t>
+    <t>Ref_05</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +588,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>1005</v>

--- a/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
+++ b/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA967D3-44E9-4772-9720-7DDE2B17EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17E367D-D3B8-42DF-8F0F-C0E92CE5E755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2">
         <v>1004</v>
@@ -587,9 +587,7 @@
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2">
-        <v>5</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>1005</v>
       </c>

--- a/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
+++ b/CoreEngine/GameData/Test/CSV/TestRefereceTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17E367D-D3B8-42DF-8F0F-C0E92CE5E755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5474C52D-9934-4B9B-A146-A35D49F1EEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,10 +506,10 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="72.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>1004</v>
@@ -587,7 +587,9 @@
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
       <c r="C6" s="2">
         <v>1005</v>
       </c>
